--- a/new-info45/web.xlsx
+++ b/new-info45/web.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\object\projectInfo\new-info45\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14475" windowHeight="10890"/>
+    <workbookView windowWidth="19140" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="14" r:id="rId1"/>
@@ -41,16 +46,16 @@
     <t>color2</t>
   </si>
   <si>
-    <t>read.combustibly.com</t>
-  </si>
-  <si>
-    <t>#e58889</t>
-  </si>
-  <si>
-    <t>sec.combustibly.com</t>
-  </si>
-  <si>
-    <t>#b57743</t>
+    <t>read.amortization.site</t>
+  </si>
+  <si>
+    <t>#707899</t>
+  </si>
+  <si>
+    <t>sec.amortization.site</t>
+  </si>
+  <si>
+    <t>#2c9678</t>
   </si>
   <si>
     <t>color1</t>
@@ -141,7 +146,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="31">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -195,18 +200,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -215,8 +213,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -380,7 +379,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="47">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,7 +448,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE58889"/>
+        <fgColor rgb="FF707899"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -461,6 +460,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF2C9678"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB57743"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -652,7 +657,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -666,21 +671,6 @@
       <top/>
       <bottom style="medium">
         <color rgb="FFE3E4E6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -785,148 +775,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -975,31 +965,31 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1430,20 +1420,20 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="20"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="23"/>
       <c r="B5" s="23"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="20"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="23"/>
       <c r="B6" s="23"/>
-      <c r="C6" s="21"/>
+      <c r="C6" s="22"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
       <c r="F6" s="24"/>
@@ -1597,8 +1587,6 @@
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1"/>
     <hyperlink ref="F17" r:id="rId2"/>
-    <hyperlink ref="A2" r:id="rId3" display="read.combustibly.com" tooltip="http://combustibly.com"/>
-    <hyperlink ref="A3" r:id="rId3" display="sec.combustibly.com" tooltip="http://combustibly.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
